--- a/DataTables/Datas/levelStep.xlsx
+++ b/DataTables/Datas/levelStep.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +65,9 @@
     <t>successHide</t>
   </si>
   <si>
+    <t>success_tip</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
     <t>步骤完成是否隐藏操作对象</t>
   </si>
   <si>
+    <t>成功反馈</t>
+  </si>
+  <si>
     <t>L01_S01</t>
   </si>
   <si>
@@ -131,10 +137,7 @@
     <t>L01_A01</t>
   </si>
   <si>
-    <t>L01_T01</t>
-  </si>
-  <si>
-    <t>L01_E01|L01_E02</t>
+    <t>L01_SAFE_DOOR_LOCK</t>
   </si>
   <si>
     <t>L01_S02</t>
@@ -143,10 +146,10 @@
     <t>L01_Tip2</t>
   </si>
   <si>
-    <t>L01_T02</t>
-  </si>
-  <si>
-    <t>L01_E03|L01_E04</t>
+    <t>L01_A02</t>
+  </si>
+  <si>
+    <t>L01_SAFE_WINDOW_OPEN</t>
   </si>
   <si>
     <t>L01_S03</t>
@@ -155,10 +158,10 @@
     <t>L01_Tip3</t>
   </si>
   <si>
-    <t>L01_T03</t>
-  </si>
-  <si>
-    <t>L01_E05|L01_E06</t>
+    <t>L01_A03</t>
+  </si>
+  <si>
+    <t>L01_SAFE_CURTAIN_OPEN</t>
   </si>
   <si>
     <t>L01_S04</t>
@@ -167,10 +170,10 @@
     <t>L01_Tip4</t>
   </si>
   <si>
-    <t>L01_T04</t>
-  </si>
-  <si>
-    <t>L01_E07|L01_E08</t>
+    <t>L01_A04</t>
+  </si>
+  <si>
+    <t>L01_SAFE_TAKEOUT_INFO</t>
   </si>
   <si>
     <t>L01_S05</t>
@@ -179,10 +182,10 @@
     <t>L01_Tip5</t>
   </si>
   <si>
-    <t>L01_T05</t>
-  </si>
-  <si>
-    <t>L01_E09|L01_E10</t>
+    <t>L01_A05</t>
+  </si>
+  <si>
+    <t>L01_SAFE_BEDSIDE_PHONE</t>
   </si>
   <si>
     <t>L01_S06</t>
@@ -191,10 +194,10 @@
     <t>L01_Tip6</t>
   </si>
   <si>
-    <t>L01_T06</t>
-  </si>
-  <si>
-    <t>L01_E11|L01_E12</t>
+    <t>L01_A06</t>
+  </si>
+  <si>
+    <t>L01_SAFE_HAND_PHONE</t>
   </si>
   <si>
     <t>L01_S07</t>
@@ -203,10 +206,10 @@
     <t>L01_Tip7</t>
   </si>
   <si>
-    <t>L01_T07</t>
-  </si>
-  <si>
-    <t>L01_E13|L01_E14</t>
+    <t>L01_A07</t>
+  </si>
+  <si>
+    <t>L01_SAFE_SOCKET_WIRE</t>
   </si>
   <si>
     <t>L01_S08</t>
@@ -215,79 +218,10 @@
     <t>L01_Tip8</t>
   </si>
   <si>
-    <t>L01_T08</t>
-  </si>
-  <si>
-    <t>L01_E15|L01_E16</t>
-  </si>
-  <si>
-    <t>L01_S09</t>
-  </si>
-  <si>
-    <t>L01_Tip9</t>
-  </si>
-  <si>
-    <t>L01_T09</t>
-  </si>
-  <si>
-    <t>L01_E17|L01_E18</t>
-  </si>
-  <si>
-    <t>L01_S10</t>
-  </si>
-  <si>
-    <t>L01_Tip10</t>
-  </si>
-  <si>
-    <t>L01_T10</t>
-  </si>
-  <si>
-    <t>L01_E19|L01_E20</t>
-  </si>
-  <si>
-    <t>L01_S11</t>
-  </si>
-  <si>
-    <t>L01_Tip11</t>
-  </si>
-  <si>
-    <t>L01_T11</t>
-  </si>
-  <si>
-    <t>L01_E21|L01_E22</t>
-  </si>
-  <si>
-    <t>L01_S12</t>
-  </si>
-  <si>
-    <t>L01_Tip12</t>
-  </si>
-  <si>
-    <t>L01_T12</t>
-  </si>
-  <si>
-    <t>L01_E23|L01_E24</t>
-  </si>
-  <si>
-    <t>L01_S13</t>
-  </si>
-  <si>
-    <t>L01_Tip13</t>
-  </si>
-  <si>
-    <t>L01_T13</t>
-  </si>
-  <si>
-    <t>L01_E25|L01_E26</t>
-  </si>
-  <si>
-    <t>L01_S14</t>
-  </si>
-  <si>
-    <t>L01_Tip14</t>
-  </si>
-  <si>
-    <t>L01_A02</t>
+    <t>L01_A08</t>
+  </si>
+  <si>
+    <t>L01_SAFE_FOOTPRINT</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1381,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="5" width="21.75" customWidth="1"/>
@@ -1460,7 +1394,7 @@
     <col min="12" max="12" width="31.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1497,520 +1431,339 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
+      <c r="M2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
       <c r="L5" t="b">
         <v>1</v>
       </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
-        <v>43</v>
-      </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
+      <c r="M7" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
-        <v>47</v>
-      </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
+      <c r="M8" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="B9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
-        <v>51</v>
-      </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
+      <c r="M9" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>55</v>
-      </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
+      <c r="M10" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="B11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
-      <c r="K11" t="s">
-        <v>59</v>
-      </c>
       <c r="L11" t="b">
         <v>1</v>
       </c>
+      <c r="M11" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
-      <c r="K12" t="s">
-        <v>63</v>
-      </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="B13" t="s">
+      <c r="M12" t="s">
         <v>64</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="s">
-        <v>75</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
-        <v>79</v>
-      </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18"/>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
